--- a/ExcelTable/RestaurantTable.xlsx
+++ b/ExcelTable/RestaurantTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\TileSystem\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60509DD9-5954-4BEC-8345-415B73F4A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4116B811-E34D-4C80-9286-EA83D733C573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30120" yWindow="2385" windowWidth="22665" windowHeight="12945" tabRatio="894" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="18" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="81">
   <si>
     <t>int</t>
   </si>
@@ -87,34 +87,22 @@
     <t>Table</t>
   </si>
   <si>
-    <t>Table_01</t>
-  </si>
-  <si>
     <t>FURNITURE_NAME_100002</t>
   </si>
   <si>
     <t>Chair</t>
   </si>
   <si>
-    <t>Chair_01</t>
-  </si>
-  <si>
     <t>FURNITURE_NAME_100003</t>
   </si>
   <si>
     <t>Stove</t>
   </si>
   <si>
-    <t>Stove_01</t>
-  </si>
-  <si>
     <t>FURNITURE_NAME_100004</t>
   </si>
   <si>
     <t>Decoration</t>
-  </si>
-  <si>
-    <t>Plant_01</t>
   </si>
   <si>
     <t>FurnitureType</t>
@@ -282,6 +270,22 @@
   </si>
   <si>
     <t>Gem</t>
+  </si>
+  <si>
+    <t>chair_1_01</t>
+  </si>
+  <si>
+    <t>SpritePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100000_01_1</t>
+  </si>
+  <si>
+    <t>table_2</t>
+  </si>
+  <si>
+    <t>deco_2</t>
   </si>
 </sst>
 </file>
@@ -353,7 +357,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -380,6 +384,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -976,7 +981,7 @@
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -991,10 +996,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>7</v>
@@ -1090,7 +1095,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -1116,13 +1121,13 @@
         <v>100002</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
+      <c r="D5" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="E5" s="6">
         <v>1</v>
@@ -1148,13 +1153,13 @@
         <v>100003</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1180,13 +1185,13 @@
         <v>100004</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1248,19 +1253,19 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>10</v>
@@ -1323,10 +1328,10 @@
         <v>200001</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>100003</v>
@@ -1349,10 +1354,10 @@
         <v>200002</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>100003</v>
@@ -1413,19 +1418,19 @@
         <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1485,10 +1490,10 @@
         <v>300001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D4" s="8">
         <v>2</v>
@@ -1511,10 +1516,10 @@
         <v>300002</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D5" s="8">
         <v>2.2000000000000002</v>
@@ -1559,13 +1564,13 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1708,16 +1713,16 @@
         <v>6</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>10</v>
@@ -1786,13 +1791,13 @@
         <v>400001</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E4" s="6">
         <v>2.5</v>
@@ -1815,13 +1820,13 @@
         <v>400002</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E5" s="6">
         <v>2</v>
@@ -1870,19 +1875,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2009,10 +2014,10 @@
         <v>10</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2051,7 +2056,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D4">
         <v>100004</v>
@@ -2065,7 +2070,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D5">
         <v>100003</v>
@@ -2079,7 +2084,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D6">
         <v>200002</v>
@@ -2093,7 +2098,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D7">
         <v>400002</v>
@@ -2145,22 +2150,22 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2220,13 +2225,13 @@
         <v>500001</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E4" s="6">
         <v>200001</v>
@@ -2235,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H4">
         <v>1000</v>
@@ -2246,13 +2251,13 @@
         <v>500002</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E5" s="6">
         <v>100001</v>
@@ -2261,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5">
         <v>5</v>

--- a/ExcelTable/RestaurantTable.xlsx
+++ b/ExcelTable/RestaurantTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\TileSystem\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4116B811-E34D-4C80-9286-EA83D733C573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0DF79F-FB27-4114-813F-53DE09898776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="1125" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="18" r:id="rId1"/>
@@ -1162,10 +1162,10 @@
         <v>80</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>5000</v>

--- a/ExcelTable/RestaurantTable.xlsx
+++ b/ExcelTable/RestaurantTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\TileSystem\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0DF79F-FB27-4114-813F-53DE09898776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC41E06-ACFB-493F-8218-C08239A3B0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="1125" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="18" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="78">
   <si>
     <t>int</t>
   </si>
@@ -84,25 +84,13 @@
     <t>FURNITURE_NAME_100001</t>
   </si>
   <si>
-    <t>Table</t>
-  </si>
-  <si>
     <t>FURNITURE_NAME_100002</t>
   </si>
   <si>
-    <t>Chair</t>
-  </si>
-  <si>
     <t>FURNITURE_NAME_100003</t>
   </si>
   <si>
-    <t>Stove</t>
-  </si>
-  <si>
     <t>FURNITURE_NAME_100004</t>
-  </si>
-  <si>
-    <t>Decoration</t>
   </si>
   <si>
     <t>FurnitureType</t>
@@ -286,6 +274,9 @@
   </si>
   <si>
     <t>deco_2</t>
+  </si>
+  <si>
+    <t>FurnitureType</t>
   </si>
 </sst>
 </file>
@@ -996,10 +987,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>7</v>
@@ -1028,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>1</v>
@@ -1091,11 +1082,11 @@
       <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
+      <c r="C4">
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -1121,13 +1112,13 @@
         <v>100002</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E5" s="6">
         <v>1</v>
@@ -1153,13 +1144,13 @@
         <v>100003</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1185,13 +1176,13 @@
         <v>100004</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1253,19 +1244,19 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>10</v>
@@ -1328,10 +1319,10 @@
         <v>200001</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>100003</v>
@@ -1354,10 +1345,10 @@
         <v>200002</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>100003</v>
@@ -1418,19 +1409,19 @@
         <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1490,10 +1481,10 @@
         <v>300001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D4" s="8">
         <v>2</v>
@@ -1516,10 +1507,10 @@
         <v>300002</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D5" s="8">
         <v>2.2000000000000002</v>
@@ -1564,13 +1555,13 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1713,16 +1704,16 @@
         <v>6</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>10</v>
@@ -1791,13 +1782,13 @@
         <v>400001</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4" s="6">
         <v>2.5</v>
@@ -1820,13 +1811,13 @@
         <v>400002</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E5" s="6">
         <v>2</v>
@@ -1875,19 +1866,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2014,10 +2005,10 @@
         <v>10</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2056,7 +2047,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>100004</v>
@@ -2070,7 +2061,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D5">
         <v>100003</v>
@@ -2084,7 +2075,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D6">
         <v>200002</v>
@@ -2098,7 +2089,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>400002</v>
@@ -2150,22 +2141,22 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2225,13 +2216,13 @@
         <v>500001</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E4" s="6">
         <v>200001</v>
@@ -2240,7 +2231,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H4">
         <v>1000</v>
@@ -2251,13 +2242,13 @@
         <v>500002</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E5" s="6">
         <v>100001</v>
@@ -2266,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H5">
         <v>5</v>

--- a/ExcelTable/RestaurantTable.xlsx
+++ b/ExcelTable/RestaurantTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\TileSystem\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC41E06-ACFB-493F-8218-C08239A3B0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D92618F-6F5A-44BD-8A2B-6966852F9A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="18" r:id="rId1"/>
@@ -1083,7 +1083,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
         <v>74</v>
@@ -1115,7 +1115,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>75</v>
@@ -1179,7 +1179,7 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
         <v>72</v>

--- a/ExcelTable/RestaurantTable.xlsx
+++ b/ExcelTable/RestaurantTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\TileSystem\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D92618F-6F5A-44BD-8A2B-6966852F9A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1755B934-DCCA-4A68-A0B4-B27C6564215B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31890" yWindow="2280" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="18" r:id="rId1"/>
@@ -1147,7 +1147,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
         <v>76</v>
